--- a/xls_files/Football_ScoringSheet.xlsx
+++ b/xls_files/Football_ScoringSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\paulio\source\repos\github.com\paulio84\super6\xls_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86659C55-B9A4-4C16-9609-E3CEFD4A725B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CD0E5E-F5A5-4048-8355-8ABC0CA6B84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2970" windowWidth="28800" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Groups A-C" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="138">
   <si>
     <t>Group A</t>
   </si>
@@ -442,16 +442,22 @@
     <t>Jenny</t>
   </si>
   <si>
-    <t>Canadia</t>
-  </si>
-  <si>
-    <t>Bosnia</t>
-  </si>
-  <si>
-    <t>Para</t>
-  </si>
-  <si>
-    <t>USA</t>
+    <t>Curacao</t>
+  </si>
+  <si>
+    <t>Holland</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Ivory Coast</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Tunisia</t>
   </si>
 </sst>
 </file>
@@ -6721,20 +6727,20 @@
         <v>111</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>132</v>
+        <v>53</v>
       </c>
       <c r="D3" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E3" s="9">
         <v>1</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G3" s="6" t="str">
         <f>IF(AND(D3=E3), "D", IF(AND(D3&gt;E3), "H W", "A W"))</f>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="7" t="s">
@@ -6774,29 +6780,29 @@
         <v>112</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D4" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>134</v>
       </c>
       <c r="G4" s="6" t="str">
         <f t="shared" ref="G4:G6" si="0">IF(AND(D4=E4), "D", IF(AND(D4&gt;E4), "H W", "A W"))</f>
-        <v>H W</v>
+        <v>D</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>116</v>
       </c>
       <c r="K4" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L4" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="9"/>
       <c r="N4" s="11" t="str">
@@ -6805,13 +6811,13 @@
       </c>
       <c r="O4" s="12">
         <f>IF(AND(K4=$D$3,L4=$E$3), 3, IF(EXACT(N4,$G$3),2,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="10" t="s">
         <v>116</v>
       </c>
       <c r="R4" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" s="9">
         <v>0</v>
@@ -6823,30 +6829,34 @@
       </c>
       <c r="V4" s="12">
         <f>IF(AND(R4=$D$4,S4=$E$4), 3, IF(EXACT(U4,$G$4),2,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>135</v>
+      </c>
       <c r="D5" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="9">
         <v>0</v>
       </c>
-      <c r="F5" s="8"/>
+      <c r="F5" s="8" t="s">
+        <v>136</v>
+      </c>
       <c r="G5" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>117</v>
       </c>
       <c r="K5" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="9">
         <v>0</v>
@@ -6858,7 +6868,7 @@
       </c>
       <c r="O5" s="12">
         <f t="shared" ref="O5:O13" si="2">IF(AND(K5=$D$3,L5=$E$3), 3, IF(EXACT(N5,$G$3),2,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="10" t="s">
         <v>117</v>
@@ -6867,7 +6877,7 @@
         <v>3</v>
       </c>
       <c r="S5" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T5" s="9"/>
       <c r="U5" s="11" t="str">
@@ -6876,48 +6886,52 @@
       </c>
       <c r="V5" s="12">
         <f t="shared" ref="V5:V13" si="4">IF(AND(R5=$D$4,S5=$E$4), 3, IF(EXACT(U5,$G$4),2,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="8"/>
+      <c r="C6" s="8" t="s">
+        <v>48</v>
+      </c>
       <c r="D6" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="9">
-        <v>0</v>
-      </c>
-      <c r="F6" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>137</v>
+      </c>
       <c r="G6" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>118</v>
       </c>
       <c r="K6" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="9"/>
       <c r="N6" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>A W</v>
+        <v>H W</v>
       </c>
       <c r="O6" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="10" t="s">
         <v>118</v>
       </c>
       <c r="R6" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" s="9">
         <v>1</v>
@@ -6925,7 +6939,7 @@
       <c r="T6" s="9"/>
       <c r="U6" s="11" t="str">
         <f t="shared" si="3"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="V6" s="12">
         <f t="shared" si="4"/>
@@ -6937,25 +6951,25 @@
         <v>121</v>
       </c>
       <c r="K7" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L7" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>A W</v>
+        <v>H W</v>
       </c>
       <c r="O7" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="10" t="s">
         <v>121</v>
       </c>
       <c r="R7" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" s="9">
         <v>2</v>
@@ -6963,11 +6977,11 @@
       <c r="T7" s="9"/>
       <c r="U7" s="11" t="str">
         <f t="shared" si="3"/>
-        <v>A W</v>
+        <v>D</v>
       </c>
       <c r="V7" s="12">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6975,19 +6989,19 @@
         <v>131</v>
       </c>
       <c r="K8" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>A W</v>
+        <v>H W</v>
       </c>
       <c r="O8" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="10" t="s">
         <v>131</v>
@@ -6996,7 +7010,7 @@
         <v>3</v>
       </c>
       <c r="S8" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T8" s="9"/>
       <c r="U8" s="11" t="str">
@@ -7005,7 +7019,7 @@
       </c>
       <c r="V8" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7013,33 +7027,33 @@
         <v>122</v>
       </c>
       <c r="K9" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="O9" s="12">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="10" t="s">
         <v>122</v>
       </c>
       <c r="R9" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S9" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T9" s="9"/>
       <c r="U9" s="11" t="str">
         <f t="shared" si="3"/>
-        <v>A W</v>
+        <v>H W</v>
       </c>
       <c r="V9" s="12">
         <f t="shared" si="4"/>
@@ -7054,7 +7068,7 @@
         <v>6</v>
       </c>
       <c r="L10" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="11" t="str">
@@ -7063,7 +7077,7 @@
       </c>
       <c r="O10" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="10" t="s">
         <v>123</v>
@@ -7072,7 +7086,7 @@
         <v>5</v>
       </c>
       <c r="S10" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T10" s="9"/>
       <c r="U10" s="11" t="str">
@@ -7081,7 +7095,7 @@
       </c>
       <c r="V10" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7089,7 +7103,7 @@
         <v>124</v>
       </c>
       <c r="K11" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" s="9">
         <v>0</v>
@@ -7101,16 +7115,16 @@
       </c>
       <c r="O11" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="10" t="s">
         <v>124</v>
       </c>
       <c r="R11" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S11" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="9"/>
       <c r="U11" s="11" t="str">
@@ -7119,7 +7133,7 @@
       </c>
       <c r="V11" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7127,7 +7141,7 @@
         <v>125</v>
       </c>
       <c r="K12" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L12" s="9">
         <v>1</v>
@@ -7139,16 +7153,16 @@
       </c>
       <c r="O12" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="10" t="s">
         <v>125</v>
       </c>
       <c r="R12" s="9">
+        <v>4</v>
+      </c>
+      <c r="S12" s="9">
         <v>3</v>
-      </c>
-      <c r="S12" s="9">
-        <v>2</v>
       </c>
       <c r="T12" s="9"/>
       <c r="U12" s="11" t="str">
@@ -7157,7 +7171,7 @@
       </c>
       <c r="V12" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7165,10 +7179,10 @@
         <v>126</v>
       </c>
       <c r="K13" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L13" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="9"/>
       <c r="N13" s="11" t="str">
@@ -7177,7 +7191,7 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="10" t="s">
         <v>126</v>
@@ -7186,7 +7200,7 @@
         <v>3</v>
       </c>
       <c r="S13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T13" s="9"/>
       <c r="U13" s="11" t="str">
@@ -7195,7 +7209,7 @@
       </c>
       <c r="V13" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7208,12 +7222,8 @@
     </row>
     <row r="16" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J16" s="10"/>
-      <c r="K16" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>120</v>
-      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
       <c r="M16" s="7"/>
       <c r="N16" s="7" t="s">
         <v>127</v>
@@ -7222,12 +7232,8 @@
         <v>18</v>
       </c>
       <c r="Q16" s="10"/>
-      <c r="R16" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="S16" s="7" t="s">
-        <v>120</v>
-      </c>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
       <c r="T16" s="7"/>
       <c r="U16" s="7" t="s">
         <v>127</v>
@@ -7240,8 +7246,12 @@
       <c r="J17" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
+      <c r="K17" s="9">
+        <v>1</v>
+      </c>
+      <c r="L17" s="9">
+        <v>1</v>
+      </c>
       <c r="M17" s="9"/>
       <c r="N17" s="11" t="str">
         <f>IF(AND(K17=L17), "D", IF(AND(K17&gt;L17), "H W", "A W"))</f>
@@ -7249,43 +7259,55 @@
       </c>
       <c r="O17" s="12">
         <f t="shared" ref="O17:O26" si="5">IF(AND(K17=$D$5,L17=$E$5), 3, IF(EXACT(N17,$G$5),2,0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
+      <c r="R17" s="9">
+        <v>2</v>
+      </c>
+      <c r="S17" s="9">
+        <v>1</v>
+      </c>
       <c r="T17" s="9"/>
       <c r="U17" s="11" t="str">
         <f>IF(AND(R17=S17), "D", IF(AND(R17&gt;S17), "H W", "A W"))</f>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="V17" s="12">
         <f>IF(AND(R17=$D$6,S17=$E$6), 3, IF(EXACT(U17,$G$6),2,0))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="10:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J18" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>2</v>
+      </c>
       <c r="M18" s="9"/>
       <c r="N18" s="11" t="str">
         <f t="shared" ref="N18:N26" si="6">IF(AND(K18=L18), "D", IF(AND(K18&gt;L18), "H W", "A W"))</f>
-        <v>D</v>
+        <v>A W</v>
       </c>
       <c r="O18" s="12">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="R18" s="9"/>
-      <c r="S18" s="9"/>
+      <c r="R18" s="9">
+        <v>1</v>
+      </c>
+      <c r="S18" s="9">
+        <v>1</v>
+      </c>
       <c r="T18" s="9"/>
       <c r="U18" s="11" t="str">
         <f t="shared" ref="U18:U26" si="7">IF(AND(R18=S18), "D", IF(AND(R18&gt;S18), "H W", "A W"))</f>
@@ -7293,15 +7315,19 @@
       </c>
       <c r="V18" s="12">
         <f t="shared" ref="V18:V26" si="8">IF(AND(R18=$D$6,S18=$E$6), 3, IF(EXACT(U18,$G$6),2,0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="10:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J19" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
+      <c r="K19" s="9">
+        <v>1</v>
+      </c>
+      <c r="L19" s="9">
+        <v>1</v>
+      </c>
       <c r="M19" s="9"/>
       <c r="N19" s="11" t="str">
         <f t="shared" si="6"/>
@@ -7309,13 +7335,17 @@
       </c>
       <c r="O19" s="12">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="R19" s="9"/>
-      <c r="S19" s="9"/>
+      <c r="R19" s="9">
+        <v>1</v>
+      </c>
+      <c r="S19" s="9">
+        <v>1</v>
+      </c>
       <c r="T19" s="9"/>
       <c r="U19" s="11" t="str">
         <f t="shared" si="7"/>
@@ -7323,15 +7353,19 @@
       </c>
       <c r="V19" s="12">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="10:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J20" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
+      <c r="K20" s="9">
+        <v>1</v>
+      </c>
+      <c r="L20" s="9">
+        <v>1</v>
+      </c>
       <c r="M20" s="9"/>
       <c r="N20" s="11" t="str">
         <f t="shared" si="6"/>
@@ -7339,33 +7373,41 @@
       </c>
       <c r="O20" s="12">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="R20" s="9"/>
-      <c r="S20" s="9"/>
+      <c r="R20" s="9">
+        <v>3</v>
+      </c>
+      <c r="S20" s="9">
+        <v>1</v>
+      </c>
       <c r="T20" s="9"/>
       <c r="U20" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="V20" s="12">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="10:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J21" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
+      <c r="K21" s="9">
+        <v>1</v>
+      </c>
+      <c r="L21" s="9">
+        <v>0</v>
+      </c>
       <c r="M21" s="9"/>
       <c r="N21" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="O21" s="12">
         <f t="shared" si="5"/>
@@ -7374,24 +7416,32 @@
       <c r="Q21" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="R21" s="9"/>
-      <c r="S21" s="9"/>
+      <c r="R21" s="9">
+        <v>3</v>
+      </c>
+      <c r="S21" s="9">
+        <v>1</v>
+      </c>
       <c r="T21" s="9"/>
       <c r="U21" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="V21" s="12">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="10:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J22" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
+      <c r="K22" s="9">
+        <v>2</v>
+      </c>
+      <c r="L22" s="9">
+        <v>2</v>
+      </c>
       <c r="M22" s="9"/>
       <c r="N22" s="11" t="str">
         <f t="shared" si="6"/>
@@ -7399,29 +7449,37 @@
       </c>
       <c r="O22" s="12">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="R22" s="9"/>
-      <c r="S22" s="9"/>
+      <c r="R22" s="9">
+        <v>3</v>
+      </c>
+      <c r="S22" s="9">
+        <v>0</v>
+      </c>
       <c r="T22" s="9"/>
       <c r="U22" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="V22" s="12">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="10:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J23" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
+      <c r="K23" s="9">
+        <v>3</v>
+      </c>
+      <c r="L23" s="9">
+        <v>3</v>
+      </c>
       <c r="M23" s="9"/>
       <c r="N23" s="11" t="str">
         <f t="shared" si="6"/>
@@ -7429,29 +7487,37 @@
       </c>
       <c r="O23" s="12">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="R23" s="9"/>
-      <c r="S23" s="9"/>
+      <c r="R23" s="9">
+        <v>2</v>
+      </c>
+      <c r="S23" s="9">
+        <v>5</v>
+      </c>
       <c r="T23" s="9"/>
       <c r="U23" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>D</v>
+        <v>A W</v>
       </c>
       <c r="V23" s="12">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="10:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
+      <c r="K24" s="9">
+        <v>2</v>
+      </c>
+      <c r="L24" s="9">
+        <v>2</v>
+      </c>
       <c r="M24" s="9"/>
       <c r="N24" s="11" t="str">
         <f t="shared" si="6"/>
@@ -7459,59 +7525,75 @@
       </c>
       <c r="O24" s="12">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
+      <c r="R24" s="9">
+        <v>2</v>
+      </c>
+      <c r="S24" s="9">
+        <v>1</v>
+      </c>
       <c r="T24" s="9"/>
       <c r="U24" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="10:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J25" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
+      <c r="K25" s="9">
+        <v>2</v>
+      </c>
+      <c r="L25" s="9">
+        <v>1</v>
+      </c>
       <c r="M25" s="9"/>
       <c r="N25" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="O25" s="12">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
+      <c r="R25" s="9">
+        <v>3</v>
+      </c>
+      <c r="S25" s="9">
+        <v>1</v>
+      </c>
       <c r="T25" s="9"/>
       <c r="U25" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="V25" s="12">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="10:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J26" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
+      <c r="K26" s="9">
+        <v>2</v>
+      </c>
+      <c r="L26" s="9">
+        <v>2</v>
+      </c>
       <c r="M26" s="9"/>
       <c r="N26" s="11" t="str">
         <f t="shared" si="6"/>
@@ -7519,21 +7601,25 @@
       </c>
       <c r="O26" s="12">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
+      <c r="R26" s="9">
+        <v>3</v>
+      </c>
+      <c r="S26" s="9">
+        <v>1</v>
+      </c>
       <c r="T26" s="9"/>
       <c r="U26" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="8"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/xls_files/Football_ScoringSheet.xlsx
+++ b/xls_files/Football_ScoringSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\paulio\source\repos\github.com\paulio84\super6\xls_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5DB10B-D177-48E0-811D-80653931167B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86971B84-9A43-4693-9A2D-92FD9EA08E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="2415" windowWidth="29715" windowHeight="16965" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31470" yWindow="1260" windowWidth="28800" windowHeight="18255" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Groups A-C" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="137">
   <si>
     <t>Group A</t>
   </si>
@@ -442,22 +442,19 @@
     <t>Jenny</t>
   </si>
   <si>
-    <t>Iran</t>
-  </si>
-  <si>
-    <t>Saudi</t>
-  </si>
-  <si>
-    <t>Uruguay</t>
-  </si>
-  <si>
-    <t>Cape Verde</t>
-  </si>
-  <si>
-    <t>New Zealand</t>
-  </si>
-  <si>
-    <t>Egypt</t>
+    <t>Uzbek</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>DR Congo</t>
   </si>
 </sst>
 </file>
@@ -6727,10 +6724,10 @@
         <v>111</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D3" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" s="9">
         <v>0</v>
@@ -6740,7 +6737,7 @@
       </c>
       <c r="G3" s="6" t="str">
         <f>IF(AND(D3=E3), "D", IF(AND(D3&gt;E3), "H W", "A W"))</f>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="7" t="s">
@@ -6780,10 +6777,10 @@
         <v>112</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D4" s="9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4" s="9">
         <v>0</v>
@@ -6793,13 +6790,13 @@
       </c>
       <c r="G4" s="6" t="str">
         <f t="shared" ref="G4:G6" si="0">IF(AND(D4=E4), "D", IF(AND(D4&gt;E4), "H W", "A W"))</f>
-        <v>H W</v>
+        <v>D</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>116</v>
       </c>
       <c r="K4" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L4" s="9">
         <v>0</v>
@@ -6811,13 +6808,13 @@
       </c>
       <c r="O4" s="12">
         <f>IF(AND(K4=$D$3,L4=$E$3), 3, IF(EXACT(N4,$G$3),2,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="10" t="s">
         <v>116</v>
       </c>
       <c r="R4" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S4" s="9">
         <v>0</v>
@@ -6829,7 +6826,7 @@
       </c>
       <c r="V4" s="12">
         <f>IF(AND(R4=$D$4,S4=$E$4), 3, IF(EXACT(U4,$G$4),2,0))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6840,23 +6837,23 @@
         <v>134</v>
       </c>
       <c r="D5" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="G5" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>D</v>
+        <v>A W</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>117</v>
       </c>
       <c r="K5" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L5" s="9">
         <v>0</v>
@@ -6868,13 +6865,13 @@
       </c>
       <c r="O5" s="12">
         <f t="shared" ref="O5:O13" si="2">IF(AND(K5=$D$3,L5=$E$3), 3, IF(EXACT(N5,$G$3),2,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="10" t="s">
         <v>117</v>
       </c>
       <c r="R5" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S5" s="9">
         <v>0</v>
@@ -6886,7 +6883,7 @@
       </c>
       <c r="V5" s="12">
         <f t="shared" ref="V5:V13" si="4">IF(AND(R5=$D$4,S5=$E$4), 3, IF(EXACT(U5,$G$4),2,0))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6894,29 +6891,29 @@
         <v>128</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D6" s="9">
         <v>1</v>
       </c>
       <c r="E6" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G6" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>A W</v>
+        <v>H W</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>118</v>
       </c>
       <c r="K6" s="9">
+        <v>4</v>
+      </c>
+      <c r="L6" s="9">
         <v>1</v>
-      </c>
-      <c r="L6" s="9">
-        <v>0</v>
       </c>
       <c r="M6" s="9"/>
       <c r="N6" s="11" t="str">
@@ -6925,13 +6922,13 @@
       </c>
       <c r="O6" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="10" t="s">
         <v>118</v>
       </c>
       <c r="R6" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S6" s="9">
         <v>0</v>
@@ -6943,7 +6940,7 @@
       </c>
       <c r="V6" s="12">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6951,7 +6948,7 @@
         <v>121</v>
       </c>
       <c r="K7" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" s="9">
         <v>0</v>
@@ -6963,16 +6960,16 @@
       </c>
       <c r="O7" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="10" t="s">
         <v>121</v>
       </c>
       <c r="R7" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S7" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" s="9"/>
       <c r="U7" s="11" t="str">
@@ -6981,7 +6978,7 @@
       </c>
       <c r="V7" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6989,7 +6986,7 @@
         <v>131</v>
       </c>
       <c r="K8" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L8" s="9">
         <v>0</v>
@@ -7001,16 +6998,16 @@
       </c>
       <c r="O8" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="10" t="s">
         <v>131</v>
       </c>
       <c r="R8" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" s="9"/>
       <c r="U8" s="11" t="str">
@@ -7019,7 +7016,7 @@
       </c>
       <c r="V8" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7027,10 +7024,10 @@
         <v>122</v>
       </c>
       <c r="K9" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="11" t="str">
@@ -7039,7 +7036,7 @@
       </c>
       <c r="O9" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="10" t="s">
         <v>122</v>
@@ -7057,7 +7054,7 @@
       </c>
       <c r="V9" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7065,37 +7062,37 @@
         <v>123</v>
       </c>
       <c r="K10" s="9">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L10" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="11" t="str">
         <f t="shared" si="1"/>
-        <v>A W</v>
+        <v>H W</v>
       </c>
       <c r="O10" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="10" t="s">
         <v>123</v>
       </c>
       <c r="R10" s="9">
+        <v>4</v>
+      </c>
+      <c r="S10" s="9">
         <v>6</v>
-      </c>
-      <c r="S10" s="9">
-        <v>3</v>
       </c>
       <c r="T10" s="9"/>
       <c r="U10" s="11" t="str">
         <f t="shared" si="3"/>
-        <v>H W</v>
+        <v>A W</v>
       </c>
       <c r="V10" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7115,16 +7112,16 @@
       </c>
       <c r="O11" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="10" t="s">
         <v>124</v>
       </c>
       <c r="R11" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S11" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="9"/>
       <c r="U11" s="11" t="str">
@@ -7133,7 +7130,7 @@
       </c>
       <c r="V11" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7153,7 +7150,7 @@
       </c>
       <c r="O12" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="10" t="s">
         <v>125</v>
@@ -7162,7 +7159,7 @@
         <v>3</v>
       </c>
       <c r="S12" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T12" s="9"/>
       <c r="U12" s="11" t="str">
@@ -7171,7 +7168,7 @@
       </c>
       <c r="V12" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7191,13 +7188,13 @@
       </c>
       <c r="O13" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="10" t="s">
         <v>126</v>
       </c>
       <c r="R13" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S13" s="9">
         <v>0</v>
@@ -7209,7 +7206,7 @@
       </c>
       <c r="V13" s="12">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7247,33 +7244,33 @@
         <v>116</v>
       </c>
       <c r="K17" s="9">
+        <v>1</v>
+      </c>
+      <c r="L17" s="9">
         <v>2</v>
-      </c>
-      <c r="L17" s="9">
-        <v>0</v>
       </c>
       <c r="M17" s="9"/>
       <c r="N17" s="11" t="str">
         <f>IF(AND(K17=L17), "D", IF(AND(K17&gt;L17), "H W", "A W"))</f>
-        <v>H W</v>
+        <v>A W</v>
       </c>
       <c r="O17" s="12">
         <f t="shared" ref="O17:O26" si="5">IF(AND(K17=$D$5,L17=$E$5), 3, IF(EXACT(N17,$G$5),2,0))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="10" t="s">
         <v>116</v>
       </c>
       <c r="R17" s="9">
+        <v>2</v>
+      </c>
+      <c r="S17" s="9">
         <v>0</v>
-      </c>
-      <c r="S17" s="9">
-        <v>2</v>
       </c>
       <c r="T17" s="9"/>
       <c r="U17" s="11" t="str">
         <f>IF(AND(R17=S17), "D", IF(AND(R17&gt;S17), "H W", "A W"))</f>
-        <v>A W</v>
+        <v>H W</v>
       </c>
       <c r="V17" s="12">
         <f>IF(AND(R17=$D$6,S17=$E$6), 3, IF(EXACT(U17,$G$6),2,0))</f>
@@ -7285,33 +7282,33 @@
         <v>117</v>
       </c>
       <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
         <v>3</v>
-      </c>
-      <c r="L18" s="9">
-        <v>0</v>
       </c>
       <c r="M18" s="9"/>
       <c r="N18" s="11" t="str">
         <f t="shared" ref="N18:N26" si="6">IF(AND(K18=L18), "D", IF(AND(K18&gt;L18), "H W", "A W"))</f>
-        <v>H W</v>
+        <v>A W</v>
       </c>
       <c r="O18" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="10" t="s">
         <v>117</v>
       </c>
       <c r="R18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S18" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T18" s="9"/>
       <c r="U18" s="11" t="str">
         <f t="shared" ref="U18:U26" si="7">IF(AND(R18=S18), "D", IF(AND(R18&gt;S18), "H W", "A W"))</f>
-        <v>A W</v>
+        <v>H W</v>
       </c>
       <c r="V18" s="12">
         <f t="shared" ref="V18:V26" si="8">IF(AND(R18=$D$6,S18=$E$6), 3, IF(EXACT(U18,$G$6),2,0))</f>
@@ -7323,33 +7320,33 @@
         <v>118</v>
       </c>
       <c r="K19" s="9">
+        <v>1</v>
+      </c>
+      <c r="L19" s="9">
         <v>3</v>
-      </c>
-      <c r="L19" s="9">
-        <v>0</v>
       </c>
       <c r="M19" s="9"/>
       <c r="N19" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>H W</v>
+        <v>A W</v>
       </c>
       <c r="O19" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="10" t="s">
         <v>118</v>
       </c>
       <c r="R19" s="9">
+        <v>2</v>
+      </c>
+      <c r="S19" s="9">
         <v>0</v>
-      </c>
-      <c r="S19" s="9">
-        <v>1</v>
       </c>
       <c r="T19" s="9"/>
       <c r="U19" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>A W</v>
+        <v>H W</v>
       </c>
       <c r="V19" s="12">
         <f t="shared" si="8"/>
@@ -7361,19 +7358,19 @@
         <v>121</v>
       </c>
       <c r="K20" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M20" s="9"/>
       <c r="N20" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>H W</v>
+        <v>A W</v>
       </c>
       <c r="O20" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="10" t="s">
         <v>121</v>
@@ -7399,25 +7396,25 @@
         <v>131</v>
       </c>
       <c r="K21" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21" s="9"/>
       <c r="N21" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>H W</v>
+        <v>A W</v>
       </c>
       <c r="O21" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="10" t="s">
         <v>131</v>
       </c>
       <c r="R21" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S21" s="9">
         <v>0</v>
@@ -7429,7 +7426,7 @@
       </c>
       <c r="V21" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="10:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7437,28 +7434,28 @@
         <v>122</v>
       </c>
       <c r="K22" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M22" s="9"/>
       <c r="N22" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>H W</v>
+        <v>A W</v>
       </c>
       <c r="O22" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="10" t="s">
         <v>122</v>
       </c>
       <c r="R22" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S22" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T22" s="9"/>
       <c r="U22" s="11" t="str">
@@ -7475,10 +7472,10 @@
         <v>123</v>
       </c>
       <c r="K23" s="9">
+        <v>6</v>
+      </c>
+      <c r="L23" s="9">
         <v>5</v>
-      </c>
-      <c r="L23" s="9">
-        <v>1</v>
       </c>
       <c r="M23" s="9"/>
       <c r="N23" s="11" t="str">
@@ -7496,12 +7493,12 @@
         <v>2</v>
       </c>
       <c r="S23" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T23" s="9"/>
       <c r="U23" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>A W</v>
+        <v>H W</v>
       </c>
       <c r="V23" s="12">
         <f t="shared" si="8"/>
@@ -7516,16 +7513,16 @@
         <v>1</v>
       </c>
       <c r="L24" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" s="9"/>
       <c r="N24" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>H W</v>
+        <v>A W</v>
       </c>
       <c r="O24" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="10" t="s">
         <v>124</v>
@@ -7534,16 +7531,16 @@
         <v>1</v>
       </c>
       <c r="S24" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T24" s="9"/>
       <c r="U24" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>A W</v>
+        <v>H W</v>
       </c>
       <c r="V24" s="12">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="10:22" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7551,15 +7548,15 @@
         <v>125</v>
       </c>
       <c r="K25" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M25" s="9"/>
       <c r="N25" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>A W</v>
+        <v>D</v>
       </c>
       <c r="O25" s="12">
         <f t="shared" si="5"/>
@@ -7569,15 +7566,15 @@
         <v>125</v>
       </c>
       <c r="R25" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S25" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T25" s="9"/>
       <c r="U25" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>H W</v>
+        <v>D</v>
       </c>
       <c r="V25" s="12">
         <f t="shared" si="8"/>
@@ -7589,37 +7586,37 @@
         <v>126</v>
       </c>
       <c r="K26" s="9">
+        <v>0</v>
+      </c>
+      <c r="L26" s="9">
         <v>2</v>
-      </c>
-      <c r="L26" s="9">
-        <v>0</v>
       </c>
       <c r="M26" s="9"/>
       <c r="N26" s="11" t="str">
         <f t="shared" si="6"/>
-        <v>H W</v>
+        <v>A W</v>
       </c>
       <c r="O26" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="10" t="s">
         <v>126</v>
       </c>
       <c r="R26" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" s="9"/>
       <c r="U26" s="11" t="str">
         <f t="shared" si="7"/>
-        <v>D</v>
+        <v>H W</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
